--- a/光伏配储项目/电价数据/2026/卓山站.xlsx
+++ b/光伏配储项目/电价数据/2026/卓山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55771</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.56581</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6911499999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.27621</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.02519</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.8399099999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44045</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39517</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.55835</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>1.05263</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.8009500000000001</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.7909299999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.5743400000000001</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.8925299999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.9184600000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.43893</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.48183</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.27203</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.28752</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.38335</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.81616</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.8627400000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.55065</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.84584</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>1.18944</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.55195</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.5764900000000001</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.92647</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.45463</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.93672</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.87261</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1.15074</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>1.09998</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.24112</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.56833</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.68229</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.83162</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.5045</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.35272</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.15958</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.4102</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.63709</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.25483</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.4877</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.63485</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.54026</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.39288</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.60555</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.5293</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.46996</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.89976</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47929</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.422</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.32822</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.09701</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.21871</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5362</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52262</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50626</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53672</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4967</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47108</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.57687</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.86424</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72251</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42847</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.43557</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.1126</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.30998</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.9363400000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.19657</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.18792</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.22275</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.83624</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.6439400000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.8059500000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.45867</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.45991</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.7425</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.40558</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.17176</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.00067</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.43456</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.35867</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.37477</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.65154</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.7329</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.60945</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.65752</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.4889</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.39604</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.39798</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.38342</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.18818</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.16206</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.17874</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.20266</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.71515</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.40276</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22096</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.5645</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.40201</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.48976</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.2798</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.82969</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.75844</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.90734</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33344</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51442</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5443600000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5803400000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.47063</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.48486</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44255</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7920499999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.89027</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.18878</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.9269500000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.89244</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.77652</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.63788</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.63344</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.43354</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.8385199999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.2974</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.78217</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.80814</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.3407</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.24132</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.39144</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.9002899999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.17013</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.40964</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.40223</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.99874</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.58469</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.49123</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.71146</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.31948</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.19338</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.39699</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.70792</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.5458</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.38352</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.26695</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.24255</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.71178</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.42809</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.43238</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.79077</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.46774</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.4389</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.24861</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.24332</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.26419</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.25025</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.43494</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.3476</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.47534</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.18675</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.85846</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.82035</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.58616</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.27251</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.69364</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.62424</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6309900000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.77455</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.7583799999999999</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.42293</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48149</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.7486</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.75927</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.99542</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.35546</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.51014</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.00306</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.75224</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.70955</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9665499999999999</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.06238</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.33508</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.49034</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.18087</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.49083</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.82425</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.09504</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.57613</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.5345599999999999</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.7587200000000001</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.19266</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.26659</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.36112</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.37284</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.32013</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.20529</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.08847</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>1.05242</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.54571</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.68045</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.93364</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.47439</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.96924</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.28919</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.33134</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.20563</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.38775</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.46187</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.50532</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.3865</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.47041</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.29544</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.22456</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18662</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.37315</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.44792</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.43458</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.40883</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.26767</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.8493999999999999</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5816399999999999</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.86402</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32404</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.7859299999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.53384</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.41239</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.52367</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.54852</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.57269</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.4754</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.79604</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.9410700000000001</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.68372</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.77965</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.8072699999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.9386100000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.7836799999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.61198</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5997400000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.65912</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.5249400000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.19535</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.59127</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5866</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.48472</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.74314</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5690599999999999</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.54147</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.54349</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.54183</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.68857</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.55802</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5489299999999999</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.52208</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38429</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.37624</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.16856</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.17966</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.65006</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.61356</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.43135</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.08367000000000001</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04364</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04174</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.09086</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04037</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04232</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04076</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.46379</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.53988</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.42198</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.4664</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.41729</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33592</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.44211</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.8933300000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.05389</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.80148</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.77608</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.78661</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.87839</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1.11931</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.54784</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.5032099999999999</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.83894</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.8487899999999999</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>1.0551</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.7030700000000001</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.61619</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.8211900000000001</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.8746799999999999</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.7442000000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.67774</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.8041699999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.8041699999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.83775</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.66901</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.8252200000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.10243</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.57256</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.61236</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.62713</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.9439</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.55074</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.17797</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.57154</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.58555</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.85899</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78771</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7884</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88102</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5059399999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41637</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46457</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22348</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6394099999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54242</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45618</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43836</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41878</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6013200000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43824</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.57114</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.67125</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.06867</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6975</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.61994</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.58629</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.05509</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.36198</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.33591</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.26355</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.57187</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.7919400000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.59626</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.6878</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.6023099999999999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>1.17406</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8478300000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7942400000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.70302</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.62936</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.20514</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.97435</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.72594</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.72885</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.51324</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.70265</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.72396</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.7482799999999999</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.67648</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.72356</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.7599900000000001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.67173</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.72572</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.7178600000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.59799</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.70384</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.74586</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.9158200000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.7241599999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.88966</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.74158</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.73022</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.72419</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.69812</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.67559</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.66515</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.67715</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.5425</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.51736</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35171</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561900000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4768</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5391900000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.79088</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.6450199999999999</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.69923</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.8774299999999999</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>1.06295</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.38712</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9949</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.64801</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.19547</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>1.00527</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>1.12892</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.03278</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.7351799999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.97925</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.26482</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.59968</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>1.06696</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.73476</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.04854</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.91096</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.49167</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.94263</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.98245</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.71957</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.87751</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.44047</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.42936</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.49437</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.45412</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42607</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.22534</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.54804</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953600000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.86145</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.45935</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.88875</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.32926</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.01059</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.74129</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.7024</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7972899999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.71006</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.45567</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.25315</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.76436</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.99836</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.7285499999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.61976</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.3079</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.22515</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.19421</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.19482</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.9858899999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.67106</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.69702</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.9482</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.65917</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.8420299999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.21417</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.21776</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.97335</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.07182</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.02703</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.25888</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.35814</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>1.0362</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.35125</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.7628</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>1.14884</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.18558</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.35462</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>1.13252</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.17704</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.73984</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.09789</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.15251</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.25797</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>1.05924</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>1.04687</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.28075</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1.13366</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.2049</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.8438099999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32463</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.46494</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.40158</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.85084</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71885</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.44898</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.48404</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.47563</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.47731</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.41813</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.48282</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.48434</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6982699999999999</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44849</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45808</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54206</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.58441</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26697</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.49838</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.72965</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6223099999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6203099999999999</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.83599</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.24778</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.14551</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.83938</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.44831</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39525</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.69311</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9257799999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.14801</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.10335</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.9992300000000001</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.53737</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42778</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.4958399999999999</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.43168</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.58078</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.47669</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.78644</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.06874</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.05862</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>1.04734</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.04911</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.53601</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.58054</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9298999999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.0687</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.9956900000000001</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.69867</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.6914</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.75873</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.77913</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.27248</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7454299999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.32298</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.47896</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.20919</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.04051</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.69111</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.67409</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.70767</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.72103</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.71611</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.69314</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.71762</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20598</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.75061</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.74781</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.75557</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.76371</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.67903</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.00394</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.11112</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.74164</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.75006</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.74387</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.77361</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8613999999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.70126</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.47612</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.09262</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.47858</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34888</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.13742</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.4357200000000001</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.79123</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49742</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.52996</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.53987</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.46061</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.9719</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.5298</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.24438</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.88859</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.75248</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.46558</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.4987200000000001</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.51487</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45968</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36206</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40294</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.46192</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.79079</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5347999999999999</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42844</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5652</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.43264</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.46322</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.69589</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45642</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45829</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40912</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65185</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83141</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43663</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5117699999999999</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.75027</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.75566</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.49985</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.52991</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.49679</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7018300000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7486499999999999</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.54555</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.49624</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.44684</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.00314</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.45364</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.41958</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.07049</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.11027</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.05852</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.10107</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.11872</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.00949</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.18496</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.13328</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.12069</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.18322</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84441</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.18609</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84574</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.3336</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.88706</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.56242</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.74529</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9349400000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.65213</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.36977</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.69403</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.20668</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.78296</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.64548</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.3054</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40345</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40634</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44939</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55951</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.58966</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46937</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.58188</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.8773</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.4133</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.46813</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.79761</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.48729</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.06243</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.72035</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.54418</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.53728</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.6024700000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.65998</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.85424</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.33816</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.79037</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1.08774</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.77151</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>1.11029</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>1.04218</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.24311</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.24429</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.59284</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.42106</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.49739</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.35518</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.31528</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.6469</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.08898</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4695</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.18512</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6548099999999999</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45751</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43662</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.45391</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.51513</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.56909</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.55106</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.7894500000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.77327</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.76258</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.47647</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.18558</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.6768</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.83946</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.26788</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.34842</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.5042300000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.2349</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5507799999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.19207</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.56149</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.56564</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42528</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.52623</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.50332</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.48361</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.54138</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5092</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45934</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.57098</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.55376</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.6626000000000001</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.78807</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.20569</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.59784</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.42992</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.43663</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.4623</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.5452</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.50873</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.46424</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.51706</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.6472100000000001</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.52019</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.47427</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.47526</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.6033500000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.47316</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.47129</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.47863</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35149</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7908200000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.38466</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.24167</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.95596</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.45515</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.7644299999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.62161</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.54691</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.4247</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.40774</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.40701</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8464700000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.4819</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.39744</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.52746</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.16162</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.50048</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.69463</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.67462</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.55143</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.80657</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.8127300000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.5363600000000001</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.43101</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.44461</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.59096</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.4631</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.41213</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.47285</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.84493</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.47095</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.8040499999999999</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.43193</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.56886</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.23997</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.24326</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.39946</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.24422</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.17481</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.78288</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.59451</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.53649</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.63226</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.82608</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5800599999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.59817</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.83351</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.82426</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.6416799999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.53708</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.17554</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.84746</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6861499999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.82339</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.38981</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.89012</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.72825</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.45085</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1.16481</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.04204</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.13716</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.58492</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.80641</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1.12223</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.78603</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>1.15348</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.38417</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.10841</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.19957</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.19009</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.74689</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.50481</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.12098</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.79711</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3943</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34728</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.57725</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.84521</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.57109</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7928500000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.79488</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.58216</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4714</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.43808</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42688</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.43118</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.43507</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.7021000000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.62866</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.60821</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.57578</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48019</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5302899999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.53276</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.82697</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.31645</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.21618</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.12901</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.21898</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.13991</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.15817</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.77386</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.5495800000000001</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5558200000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.6264400000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.4964</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.6000700000000001</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5709299999999999</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.5456599999999999</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.58063</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6914</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.64053</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.10519</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.7153099999999999</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5707100000000001</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.51795</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.51649</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.49716</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.51549</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.49591</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.51437</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.60017</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5761000000000001</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.5811900000000001</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.51288</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.53016</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.43117</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.51525</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.58212</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.69011</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.31048</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.21685</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.68733</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.60684</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.25042</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.9169700000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.68849</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.29905</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.9835</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.52512</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.52712</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.55118</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34571</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.50976</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.49491</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.44626</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43218</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.65527</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.6281</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.71749</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.18668</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.45669</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9913099999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.13434</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.17356</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.12892</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.10224</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.13688</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.11379</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1.10589</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>1.10925</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.787</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.61325</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.09647</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.70463</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.08723</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.07792</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.05977</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.8981</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1.10274</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1.01858</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>1.08588</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.59454</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.29366</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.17469</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.11552</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.51609</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.4222</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.10987</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.20794</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.01628</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.83778</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.83658</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.88074</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.79261</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68923</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.61621</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.71738</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.83569</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.78722</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.8394199999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7978</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.49217</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.84554</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.5412400000000001</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.46863</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.19749</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.09857</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.18945</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.13972</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.19734</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.18016</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.18032</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.23412</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.2544</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.15585</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.6279</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.76974</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.78935</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.84642</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.82012</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.00822</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.23171</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.21103</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.49879</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.50506</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.32766</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.25782</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.43756</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.04343</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.47033</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.44938</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.72421</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.49158</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.49338</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.8444700000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.84497</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.84538</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3751</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27093</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.79575</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.44193</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.79799</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.28855</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.98676</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9168099999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9430700000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.04878</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.17199</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.11712</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.84714</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6853400000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.32413</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.24237</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.24701</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.12414</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.84454</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.68621</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.06708</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.78328</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.08221</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.08243</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.12396</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.07968</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5120399999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.17557</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.75549</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.6241599999999999</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15255</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.8439099999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.76822</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.16134</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.93714</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.03672</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.17754</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.25252</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.05118</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.05183</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.10659</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.0333</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.0439</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.17343</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.1539</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.17117</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.19081</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.47525</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.15608</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.27039</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.10269</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.08327</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.10891</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.15805</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.17462</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.15525</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.3076</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.77798</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.69464</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.6292300000000001</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.59924</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37552</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.62812</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.29041</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.28946</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.05058</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.49346</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51609</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37718</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8461000000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.6338400000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.79259</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.8079299999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.75748</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.03855</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.85405</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.04394</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.25659</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.44201</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.61374</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.59516</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.43829</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.70131</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.35055</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.84623</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.63472</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7534400000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.69665</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.49416</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84035</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.97136</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.41097</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.7876799999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57548</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.60993</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.73485</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.8306399999999999</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.72512</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.84161</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.71586</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.30205</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.26429</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.45412</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.26964</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.24105</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.25817</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.25346</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.2251</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20343</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.24812</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.33317</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.20638</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.22472</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20197</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.25814</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.60886</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.82612</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8015399999999999</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56298</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.32908</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84646</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84697</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.5577300000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55349</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5651499999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51461</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55275</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52018</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45929</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41162</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49339</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49782</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54508</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.51709</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.51819</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55408</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17004</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8790800000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.48587</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.36752</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.5011</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5726100000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84662</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79771</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59812</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.84629</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.5242</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.55583</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.16702</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.6974199999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55006</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.22566</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54427</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.54244</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.57741</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.7956</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5486</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.78603</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8449</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.16804</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79427</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6805399999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.26649</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17411</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.19948</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.21666</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.21382</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.81053</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.75019</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.70331</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.72992</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.74121</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.74614</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.82372</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.80808</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6559299999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.8080900000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.18226</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.85123</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60607</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.72725</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6881699999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.63717</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.62486</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.8061699999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.72122</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.9049700000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70237</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60707</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5302899999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
